--- a/data-raw/releases.xlsx
+++ b/data-raw/releases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jakethompson/Documents/GIT/packages/taylor/data-raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8E8710-338D-704B-B59F-C52C4E9B6B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{552C3B01-5484-5B41-B61E-677415AFBD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="19300" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="155">
   <si>
     <t>album_name</t>
   </si>
@@ -476,6 +476,18 @@
   </si>
   <si>
     <t>The Fate Of Ophelia</t>
+  </si>
+  <si>
+    <t>Elizabeth Taylor</t>
+  </si>
+  <si>
+    <t>I Knew It, I Knew You</t>
+  </si>
+  <si>
+    <t>Patient Zero</t>
+  </si>
+  <si>
+    <t>The Life of a Showgirl: The Encore</t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1333,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D154"/>
+  <dimension ref="A1:D158"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="48.1640625" bestFit="1" customWidth="1"/>
@@ -2838,6 +2850,44 @@
         <v>46034</v>
       </c>
     </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>148</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D155" s="1">
+        <v>46090</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B156" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D156" s="1">
+        <v>46178</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>154</v>
+      </c>
+      <c r="D157" s="1">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>154</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D158" s="1">
+        <v>46290</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D110" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
